--- a/测试用例及跟踪.xlsx
+++ b/测试用例及跟踪.xlsx
@@ -332,7 +332,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,13 +374,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -525,7 +518,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,12 +570,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,148 +823,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
